--- a/Data/FRB_all.xlsx
+++ b/Data/FRB_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Research\FRB\cosmology\FRB_cosmology\code\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8147C69-10C3-47DA-A339-DEAAEC98B728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B71ED38-3257-44F4-AD93-0723F3CD669D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7395" yWindow="840" windowWidth="19440" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -211,10 +211,6 @@
     <t>FRB 20240310A</t>
   </si>
   <si>
-    <t>Surajit…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FRB 20220204A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -328,6 +324,10 @@
   </si>
   <si>
     <t>FRB 20231123B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Surajit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -680,13 +680,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,9 +700,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>0.4012</v>
@@ -714,9 +714,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>4.3299999999999998E-2</v>
@@ -727,10 +727,13 @@
       <c r="D3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" s="4">
+        <v>262.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>0.35099999999999998</v>
@@ -742,9 +745,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5">
         <v>0.24179999999999999</v>
@@ -756,9 +759,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0.47799999999999998</v>
@@ -769,10 +772,13 @@
       <c r="D6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" s="4">
+        <v>462.24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>0.37140000000000001</v>
@@ -784,9 +790,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>0.62139999999999995</v>
@@ -797,10 +803,13 @@
       <c r="D8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8" s="4">
+        <v>623.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9">
         <v>0.3</v>
@@ -811,10 +820,13 @@
       <c r="D9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9" s="4">
+        <v>396.97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10">
         <v>8.9399999999999993E-2</v>
@@ -825,10 +837,13 @@
       <c r="D10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10" s="4">
+        <v>269.52999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11">
         <v>0.3619</v>
@@ -840,9 +855,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12">
         <v>0.2414</v>
@@ -853,10 +868,13 @@
       <c r="D12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12" s="4">
+        <v>651.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13">
         <v>0.1139</v>
@@ -867,10 +885,13 @@
       <c r="D13" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13" s="4">
+        <v>631.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14">
         <v>0.15820000000000001</v>
@@ -881,10 +902,13 @@
       <c r="D14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14" s="4">
+        <v>314.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15">
         <v>0.28470000000000001</v>
@@ -895,10 +919,13 @@
       <c r="D15" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15" s="4">
+        <v>441.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16">
         <v>0.54220000000000002</v>
@@ -910,9 +937,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17">
         <v>0.97499999999999998</v>
@@ -924,9 +951,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18">
         <v>0.23949999999999999</v>
@@ -938,9 +965,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19">
         <v>0.2505</v>
@@ -952,9 +979,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20">
         <v>0.27639999999999998</v>
@@ -966,9 +993,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21">
         <v>0.55300000000000005</v>
@@ -980,9 +1007,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22">
         <v>9.3899999999999997E-2</v>
@@ -994,9 +1021,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23">
         <v>0.53100000000000003</v>
@@ -1008,9 +1035,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24">
         <v>0.27060000000000001</v>
@@ -1022,9 +1049,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25">
         <v>0.30149999999999999</v>
@@ -1036,9 +1063,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26">
         <v>0.32700000000000001</v>
@@ -1050,9 +1077,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27">
         <v>0.127</v>
@@ -1064,9 +1091,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28">
         <v>0.45250000000000001</v>
@@ -1078,9 +1105,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29">
         <v>3.6799999999999999E-2</v>
@@ -1092,9 +1119,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B30">
         <v>0.2621</v>
@@ -1106,7 +1133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>5</v>
       </c>
@@ -1117,10 +1144,13 @@
         <v>369</v>
       </c>
       <c r="D31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E31" s="4">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>6</v>
       </c>
@@ -1131,10 +1161,13 @@
         <v>76.099999999999994</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E32" s="4">
+        <v>114.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>7</v>
       </c>
@@ -1145,10 +1178,13 @@
         <v>370</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E33" s="4">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>8</v>
       </c>
@@ -1159,10 +1195,13 @@
         <v>149.30000000000001</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E34" s="4">
+        <v>349.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>9</v>
       </c>
@@ -1173,10 +1212,13 @@
         <v>320.92</v>
       </c>
       <c r="D35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E35" s="4">
+        <v>361.42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>10</v>
       </c>
@@ -1187,10 +1229,13 @@
         <v>487.27</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E36" s="4">
+        <v>589.27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
@@ -1201,10 +1246,13 @@
         <v>83.4</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E37" s="4">
+        <v>209.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>12</v>
       </c>
@@ -1215,10 +1263,13 @@
         <v>92.5</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E38" s="4">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>13</v>
       </c>
@@ -1229,10 +1280,13 @@
         <v>306.3</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E39" s="4">
+        <v>363.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>14</v>
       </c>
@@ -1243,10 +1297,13 @@
         <v>184.5</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E40" s="4">
+        <v>221.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>15</v>
       </c>
@@ -1257,10 +1314,13 @@
         <v>193.4</v>
       </c>
       <c r="D41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E41" s="4">
+        <v>222.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>16</v>
       </c>
@@ -1271,10 +1331,13 @@
         <v>113.5</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E42" s="4">
+        <v>184.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>17</v>
       </c>
@@ -1285,10 +1348,13 @@
         <v>79.199999999999989</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E43" s="4">
+        <v>128.19999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>18</v>
       </c>
@@ -1299,10 +1365,13 @@
         <v>1091.7</v>
       </c>
       <c r="D44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E44" s="4">
+        <v>1204.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>19</v>
       </c>
@@ -1313,10 +1382,13 @@
         <v>723.8</v>
       </c>
       <c r="D45" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E45" s="4">
+        <v>760.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>20</v>
       </c>
@@ -1327,10 +1399,13 @@
         <v>301.5</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E46" s="4">
+        <v>338.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>21</v>
       </c>
@@ -1341,10 +1416,13 @@
         <v>263.57</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E47" s="4">
+        <v>321.39999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>22</v>
       </c>
@@ -1355,10 +1433,13 @@
         <v>875.7</v>
       </c>
       <c r="D48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E48" s="4">
+        <v>959.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>23</v>
       </c>
@@ -1369,10 +1450,13 @@
         <v>536.70000000000005</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E49" s="4">
+        <v>593.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>24</v>
       </c>
@@ -1383,10 +1467,13 @@
         <v>465</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E50" s="4">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>25</v>
       </c>
@@ -1397,10 +1484,13 @@
         <v>462.22</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E51" s="4">
+        <v>506.92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>26</v>
       </c>
@@ -1411,10 +1501,13 @@
         <v>307.2</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E52" s="4">
+        <v>332.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>27</v>
       </c>
@@ -1425,10 +1518,13 @@
         <v>264.5</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E53" s="4">
+        <v>297.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>28</v>
       </c>
@@ -1439,10 +1535,13 @@
         <v>156.20000000000002</v>
       </c>
       <c r="D54" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E54" s="4">
+        <v>201.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>29</v>
       </c>
@@ -1453,10 +1552,13 @@
         <v>353.1</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E55" s="4">
+        <v>380.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>30</v>
       </c>
@@ -1467,10 +1569,13 @@
         <v>541.79999999999995</v>
       </c>
       <c r="D56" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E56" s="4">
+        <v>577.79999999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>31</v>
       </c>
@@ -1481,10 +1586,13 @@
         <v>181.62</v>
       </c>
       <c r="D57" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E57" s="4">
+        <v>433.55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>32</v>
       </c>
@@ -1495,10 +1603,13 @@
         <v>290.32</v>
       </c>
       <c r="D58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E58" s="4">
+        <v>413.52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>33</v>
       </c>
@@ -1509,10 +1620,13 @@
         <v>695.6</v>
       </c>
       <c r="D59" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E59" s="4">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>34</v>
       </c>
@@ -1523,10 +1637,13 @@
         <v>342.8</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E60" s="4">
+        <v>384.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>35</v>
       </c>
@@ -1537,10 +1654,13 @@
         <v>49.069999999999936</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E61" s="4">
+        <v>565.16999999999996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>36</v>
       </c>
@@ -1551,10 +1671,13 @@
         <v>522.57999999999993</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E62" s="4">
+        <v>578.78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>37</v>
       </c>
@@ -1565,10 +1688,13 @@
         <v>460.14699999999999</v>
       </c>
       <c r="D63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E63" s="4">
+        <v>500.14699999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>38</v>
       </c>
@@ -1579,10 +1705,13 @@
         <v>130.69999999999999</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E64" s="4">
+        <v>251.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>39</v>
       </c>
@@ -1593,10 +1722,13 @@
         <v>192.33</v>
       </c>
       <c r="D65" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E65" s="4">
+        <v>234.83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>40</v>
       </c>
@@ -1607,10 +1739,13 @@
         <v>573.20000000000005</v>
       </c>
       <c r="D66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E66" s="4">
+        <v>636.20000000000005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>41</v>
       </c>
@@ -1621,10 +1756,13 @@
         <v>178.9</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E67" s="4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>42</v>
       </c>
@@ -1635,10 +1773,13 @@
         <v>561</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E68" s="4">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>43</v>
       </c>
@@ -1649,10 +1790,13 @@
         <v>363.57</v>
       </c>
       <c r="D69" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E69" s="4">
+        <v>499.27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>44</v>
       </c>
@@ -1663,10 +1807,13 @@
         <v>418.5</v>
       </c>
       <c r="D70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E70" s="4">
+        <v>449.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>45</v>
       </c>
@@ -1677,10 +1824,13 @@
         <v>1427</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E71" s="4">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>46</v>
       </c>
@@ -1691,10 +1841,13 @@
         <v>259.39999999999998</v>
       </c>
       <c r="D72" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E72" s="4">
+        <v>290.39999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>47</v>
       </c>
@@ -1705,10 +1858,13 @@
         <v>94.460000000000008</v>
       </c>
       <c r="D73" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E73" s="4">
+        <v>219.46</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>48</v>
       </c>
@@ -1719,10 +1875,13 @@
         <v>615.79999999999995</v>
       </c>
       <c r="D74" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E74" s="4">
+        <v>656.8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>49</v>
       </c>
@@ -1733,10 +1892,13 @@
         <v>308.8</v>
       </c>
       <c r="D75" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E75" s="4">
+        <v>343.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>50</v>
       </c>
@@ -1747,10 +1909,13 @@
         <v>311.39999999999998</v>
       </c>
       <c r="D76" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E76" s="4">
+        <v>361.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>51</v>
       </c>
@@ -1761,10 +1926,13 @@
         <v>361.51</v>
       </c>
       <c r="D77" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E77" s="4">
+        <v>411.51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>52</v>
       </c>
@@ -1775,10 +1943,13 @@
         <v>83.600000000000023</v>
       </c>
       <c r="D78" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E78" s="4">
+        <v>476.6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>53</v>
       </c>
@@ -1789,10 +1960,13 @@
         <v>406.1</v>
       </c>
       <c r="D79" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E79" s="4">
+        <v>440.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>54</v>
       </c>
@@ -1803,10 +1977,13 @@
         <v>184.89999999999998</v>
       </c>
       <c r="D80" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E80" s="4">
+        <v>329.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>55</v>
       </c>
@@ -1817,10 +1994,13 @@
         <v>487.70000000000005</v>
       </c>
       <c r="D81" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E81" s="4">
+        <v>527.70000000000005</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>56</v>
       </c>
@@ -1831,10 +2011,13 @@
         <v>336.5</v>
       </c>
       <c r="D82" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E82" s="4">
+        <v>374.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>57</v>
       </c>
@@ -1845,10 +2028,13 @@
         <v>252.73000000000002</v>
       </c>
       <c r="D83" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="E83" s="4">
+        <v>283.73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>58</v>
       </c>
@@ -1859,7 +2045,10 @@
         <v>565.79999999999995</v>
       </c>
       <c r="D84" t="s">
-        <v>59</v>
+        <v>88</v>
+      </c>
+      <c r="E84" s="4">
+        <v>601.79999999999995</v>
       </c>
     </row>
   </sheetData>
